--- a/output/pdf_financials_xlsx/AUME.xlsx
+++ b/output/pdf_financials_xlsx/AUME.xlsx
@@ -5052,7 +5052,7 @@
         <v>2.865212</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>2.998728</v>
+        <v>3.338296</v>
       </c>
     </row>
     <row r="93">
@@ -5352,7 +5352,7 @@
         <v>-1.751622</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>0.000245</v>
+        <v>-0.000245</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>-1.678904</v>
@@ -9438,7 +9438,11 @@
           <t>Reserves 13 3,552,142 3,360,550</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -28494,7 +28498,7 @@
         <v>-1.751622</v>
       </c>
       <c r="Q252" s="5" t="n">
-        <v>0.000245</v>
+        <v>-0.000245</v>
       </c>
       <c r="R252" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AUME.xlsx
+++ b/output/pdf_financials_xlsx/AUME.xlsx
@@ -968,31 +968,31 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000171</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.001334</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.078789</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.113422</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.044009</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.015605</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.056177</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.078489</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.075854</v>
       </c>
     </row>
     <row r="13">
@@ -1781,31 +1781,31 @@
         <v>-0.145859</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.205917</v>
+        <v>-0.206088</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.669681</v>
+        <v>-2.671015</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.508774</v>
+        <v>-5.587563</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.920369</v>
+        <v>-4.033791</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.645265</v>
+        <v>-1.689274</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.027459</v>
+        <v>-2.043064</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.76337</v>
+        <v>-1.819547</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.789985</v>
+        <v>-0.868474</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.678904</v>
+        <v>-1.754758</v>
       </c>
     </row>
     <row r="28">
@@ -1881,31 +1881,31 @@
         <v>-0.145859</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.205917</v>
+        <v>-0.206088</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.669681</v>
+        <v>-2.671015</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.508774</v>
+        <v>-5.587563</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.920369</v>
+        <v>-4.033791</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.645265</v>
+        <v>-1.689274</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.027459</v>
+        <v>-2.043064</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.76337</v>
+        <v>-1.819547</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.789985</v>
+        <v>-0.868474</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.676642</v>
+        <v>-1.752496</v>
       </c>
     </row>
     <row r="30">
@@ -1955,19 +1955,19 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1150.299137650266</v>
+        <v>-1183.578971459422</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-132.6914360465773</v>
+        <v>-136.2407836647262</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-86.96710925348755</v>
+        <v>-87.63647999780379</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-50.10771039330704</v>
+        <v>-51.70402928654261</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-23.98598827336166</v>
+        <v>-26.36911736263283</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -2119,10 +2119,10 @@
         <v>0.119579</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.07058499999999999</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.071784</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>1.095504</v>
@@ -2217,10 +2217,10 @@
         <v>0.119579</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.07058499999999999</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.071784</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>1.095504</v>
@@ -2805,10 +2805,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.008607</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.071784</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.121854</v>
@@ -20416,7 +20416,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -21264,7 +21264,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -41906,7 +41906,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -43824,7 +43824,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">

--- a/output/pdf_financials_xlsx/AUME.xlsx
+++ b/output/pdf_financials_xlsx/AUME.xlsx
@@ -1833,25 +1833,25 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.001536</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.02908</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.071892</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.215931</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.299413</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.369842</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>0.002262</v>
@@ -1884,25 +1884,25 @@
         <v>-0.206088</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.671015</v>
+        <v>-2.669479</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.587563</v>
+        <v>-5.558483</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.033791</v>
+        <v>-3.961899</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.689274</v>
+        <v>-1.473343</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.043064</v>
+        <v>-1.743651</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.819547</v>
+        <v>-1.449705</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.868474</v>
+        <v>-0.866974</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-1.752496</v>
@@ -1955,19 +1955,19 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1183.578971459422</v>
+        <v>-1162.484705689044</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-136.2407836647262</v>
+        <v>-118.8258417088872</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-87.63647999780379</v>
+        <v>-74.79326931738339</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-51.70402928654261</v>
+        <v>-41.19464337928465</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-26.36911736263283</v>
+        <v>-26.32357348216668</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -5383,28 +5383,28 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.001536</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.026587</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.071892</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.215931</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.299413</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.369842</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.002262</v>
       </c>
     </row>
     <row r="101">
@@ -5974,22 +5974,22 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.002493</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.0005820000000000001</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="O112" s="3" t="n">
         <v>0</v>
@@ -26164,7 +26164,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -26236,7 +26240,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -27370,7 +27378,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -32050,7 +32062,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -32134,7 +32150,11 @@
           <t>Loss on disposal of property and equipment 9</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -41668,7 +41688,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -46320,7 +46344,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -46824,7 +46852,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -48458,7 +48490,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AUME.xlsx
+++ b/output/pdf_financials_xlsx/AUME.xlsx
@@ -706,22 +706,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.002</v>
+        <v>0.002264</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.022103</v>
+        <v>0.042072</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.014954</v>
+        <v>0.042351</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.014959</v>
+        <v>0.033502</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.014165</v>
+        <v>0.074492</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.016404</v>
+        <v>0.069234</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.063781</v>
@@ -853,19 +853,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.002</v>
+        <v>0.002264</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.022103</v>
+        <v>0.042072</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.014954</v>
+        <v>0.042351</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.014959</v>
+        <v>0.033502</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.014165</v>
+        <v>0.074492</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.000171</v>
@@ -907,16 +907,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.022103</v>
+        <v>-0.042072</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.014954</v>
+        <v>-0.042351</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.014959</v>
+        <v>-0.033502</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.014165</v>
+        <v>-0.074492</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.206088</v>
@@ -1422,11 +1422,15 @@
       <c r="G20" s="3" t="n">
         <v>-0.30706</v>
       </c>
-      <c r="H20" s="3" t="n">
-        <v>-2.430754</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>-4.689526</v>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="3" t="n">
         <v>-3.54642</v>
@@ -1443,8 +1447,10 @@
       <c r="N20" s="3" t="n">
         <v>-0.649245</v>
       </c>
-      <c r="O20" s="3" t="n">
-        <v>-1.678904</v>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1472,10 +1478,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-0.362615</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-0.032073</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -1493,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>-1.300922</v>
       </c>
     </row>
     <row r="22">
@@ -3231,10 +3237,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>0</v>
@@ -3280,10 +3286,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>0.001536</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>0.001536</v>
       </c>
       <c r="J57" s="3" t="n">
         <v>0</v>
@@ -6524,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L123" s="3" t="n">
         <v>0</v>
@@ -6622,10 +6628,10 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-0.031912</v>
+        <v>0.9680879999999999</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-0.067692</v>
+        <v>0.052308</v>
       </c>
       <c r="L125" s="3" t="n">
         <v>-0.100271</v>
@@ -26486,7 +26492,11 @@
           <t>Deferred tax recovery 20</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -29524,7 +29534,11 @@
           <t>Deferred tax recovery 21</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -29770,7 +29784,11 @@
           <t>Private placements 14</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -30184,7 +30202,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -30268,7 +30290,11 @@
           <t>Deferred income tax recovery 22</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -30696,7 +30722,11 @@
           <t>Private placements 15</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -30946,7 +30976,11 @@
           <t>Deferred tax recovery 22</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -32416,7 +32450,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -32764,7 +32802,11 @@
           <t>Private placements 10</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -34044,7 +34086,11 @@
           <t>Private placements 11</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -40134,7 +40180,11 @@
           <t>Net loss - discontinued operations -</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -47450,7 +47500,11 @@
           <t>Net loss – discontinued operations 8</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -49088,7 +49142,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
           <t>-</t>
@@ -49586,7 +49644,11 @@
           <t>Office expenses (Note 6)</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
           <t>-</t>
@@ -50520,7 +50582,11 @@
           <t>Office expenses 19,969</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E512" s="5" t="n">
         <v>0.000264</v>
       </c>
